--- a/tests/v1/fixtures/office6m/2026-06/bank_statements/HB_B_USD_2026-05.xlsx
+++ b/tests/v1/fixtures/office6m/2026-06/bank_statements/HB_B_USD_2026-05.xlsx
@@ -684,13 +684,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>704314.35</v>
+        <v>706464.35</v>
       </c>
       <c r="E2" t="n">
         <v>-15109.41</v>
       </c>
       <c r="F2" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
     </row>
     <row r="3">
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
     </row>
     <row r="4">
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
     </row>
     <row r="5">
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
     </row>
     <row r="6">
@@ -788,13 +788,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
     </row>
     <row r="7">
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
     </row>
     <row r="8">
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
     </row>
     <row r="9">
@@ -866,13 +866,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
       <c r="E9" t="n">
         <v>600000</v>
       </c>
       <c r="F9" t="n">
-        <v>1289204.94</v>
+        <v>1291354.94</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1289204.94</v>
+        <v>1291354.94</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1289204.94</v>
+        <v>1291354.94</v>
       </c>
     </row>
     <row r="11">
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1289204.94</v>
+        <v>1291354.94</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1289204.94</v>
+        <v>1291354.94</v>
       </c>
     </row>
     <row r="12">
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1289204.94</v>
+        <v>1291354.94</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1289204.94</v>
+        <v>1291354.94</v>
       </c>
     </row>
     <row r="13">
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1289204.94</v>
+        <v>1291354.94</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1289204.94</v>
+        <v>1291354.94</v>
       </c>
     </row>
     <row r="14">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1289204.94</v>
+        <v>1291354.94</v>
       </c>
       <c r="E14" t="n">
         <v>-600000</v>
       </c>
       <c r="F14" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
     </row>
     <row r="15">
@@ -1022,13 +1022,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
     </row>
     <row r="16">
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
     </row>
     <row r="17">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
     </row>
     <row r="18">
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
     </row>
     <row r="19">
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
     </row>
     <row r="20">
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
     </row>
     <row r="21">
@@ -1178,13 +1178,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>689204.9399999999</v>
+        <v>691354.9399999999</v>
       </c>
       <c r="E21" t="n">
         <v>-15280.64</v>
       </c>
       <c r="F21" t="n">
-        <v>673924.3</v>
+        <v>676074.3</v>
       </c>
     </row>
     <row r="22">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>673924.3</v>
+        <v>676074.3</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>673924.3</v>
+        <v>676074.3</v>
       </c>
     </row>
   </sheetData>
